--- a/artfynd/A 12686-2026 artfynd.xlsx
+++ b/artfynd/A 12686-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103714357</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>745401.6044952202</v>
+        <v>745402</v>
       </c>
       <c r="R2" t="n">
-        <v>7092348.143392303</v>
+        <v>7092348</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -752,19 +747,9 @@
           <t>2022-08-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
